--- a/InputData/hydgn/EHPpUC/Electrolyzer Hydrogen Production per Unit Capacity.xlsx
+++ b/InputData/hydgn/EHPpUC/Electrolyzer Hydrogen Production per Unit Capacity.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27618"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-texas\InputData\hydgn\EHPpUC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shruti.Dayal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{0248164D-7B40-414E-BCCD-1B0B9ACA60E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3832F87D-F0A8-4CF4-A5C0-ED1E0D5C7387}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5445"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Calculations" sheetId="3" r:id="rId2"/>
     <sheet name="EHPpUC" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -28,21 +40,24 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
+    <t>EHPpUC Electrolyzer Hydrogen Production per Unit Capacity</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>Wang et al.</t>
+  </si>
+  <si>
+    <t>Quantifying the flexibility of hydrogen production systems to support large-scale renewable energy integration</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jpowsour.2018.07.101</t>
+  </si>
+  <si>
     <t>Page 388, Table 2</t>
   </si>
   <si>
-    <t>Wang et al.</t>
-  </si>
-  <si>
-    <t>Quantifying the flexibility of hydrogen production systems to support large-scale renewable energy integration</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.jpowsour.2018.07.101</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -64,15 +79,12 @@
     <t>Scenario</t>
   </si>
   <si>
+    <t>H2 Production (ton/yr)</t>
+  </si>
+  <si>
     <t>Electrolyzer Capacity (MW)</t>
   </si>
   <si>
-    <t>H2 Production (ton/yr)</t>
-  </si>
-  <si>
-    <t>EHPpUC Electrolyzer Hydrogen Production per Unit Capacity</t>
-  </si>
-  <si>
     <t>tons H2 / MW</t>
   </si>
   <si>
@@ -91,26 +103,26 @@
     <t>lb/metric ton</t>
   </si>
   <si>
+    <t xml:space="preserve">The study they are citing uses 3 scenarios of Fuel Cell Electric Vehicle adoption. Then it calculates the amount of hydrogen needed to suppor those vehicles. Then it calculates the electrolyzer capacity needed to supply that hydrogen. </t>
+  </si>
+  <si>
+    <t>So, I think it's fair, using the EPS assumptions of 24/7/365 operation, that smallest electrolyzer you would need to produce 1.39e10 annual Btu would be 1 MW.</t>
+  </si>
+  <si>
+    <t>BTU H2 / MW (annual production)</t>
+  </si>
+  <si>
+    <t>No reason to think this would be different for Texas.</t>
+  </si>
+  <si>
     <t>(BTU H2/yr) / MW</t>
-  </si>
-  <si>
-    <t>BTU H2 / MW (annual production)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The study they are citing uses 3 scenarios of Fuel Cell Electric Vehicle adoption. Then it calculates the amount of hydrogen needed to suppor those vehicles. Then it calculates the electrolyzer capacity needed to supply that hydrogen. </t>
-  </si>
-  <si>
-    <t>So, I think it's fair, using the EPS assumptions of 24/7/365 operation, that smallest electrolyzer you would need to produce 1.39e10 annual Btu would be 1 MW.</t>
-  </si>
-  <si>
-    <t>No reason to think this would be different for Texas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,12 +152,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -194,7 +200,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -208,21 +214,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -503,18 +503,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -537,90 +537,77 @@
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="25.1328125" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="5" width="14.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-    </row>
-    <row r="2" spans="1:15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -634,18 +621,8 @@
         <f>B3/C3</f>
         <v>264.14473684210526</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-    </row>
-    <row r="4" spans="1:15">
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>2</v>
       </c>
@@ -659,13 +636,8 @@
         <f>B4/C4</f>
         <v>264.14473684210526</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-    </row>
-    <row r="5" spans="1:15">
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -679,31 +651,14 @@
         <f t="shared" ref="E5" si="0">B5/C5</f>
         <v>264.14473684210526</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:15">
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.4">
-      <c r="A8" s="9">
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
         <v>60920</v>
       </c>
       <c r="B8" t="s">
@@ -713,21 +668,16 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.4">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-    </row>
-    <row r="11" spans="1:15">
+    <row r="9" spans="1:7" ht="15.6">
+      <c r="A9" s="11"/>
+      <c r="C9" s="12"/>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2204.62</v>
       </c>
@@ -735,158 +685,83 @@
         <v>20</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="C13" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="C13" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <f>E3*A12*A8</f>
         <v>35476077852.368416</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="D16" s="14"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-    </row>
-    <row r="17" spans="4:9">
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" spans="4:9">
-      <c r="D18" s="14"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-    </row>
-    <row r="19" spans="4:9">
-      <c r="D19" s="14"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-    </row>
-    <row r="20" spans="4:9">
-      <c r="D20" s="14"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-    </row>
-    <row r="21" spans="4:9">
-      <c r="D21" s="14"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-    </row>
-    <row r="22" spans="4:9">
-      <c r="D22" s="14"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="4:9">
-      <c r="D23" s="14"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-    </row>
-    <row r="24" spans="4:9">
-      <c r="D24" s="14"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-    </row>
-    <row r="25" spans="4:9">
-      <c r="D25" s="14"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-    </row>
-    <row r="26" spans="4:9">
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-    </row>
-    <row r="27" spans="4:9">
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-    </row>
-    <row r="28" spans="4:9">
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="18" spans="5:6" ht="16.5">
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="5:6" ht="16.5">
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" spans="5:6" ht="16.5">
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="5:6" ht="16.5">
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="5:6" ht="16.5">
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="5:6" ht="16.5">
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" spans="5:6" ht="16.5">
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+    </row>
+    <row r="25" spans="5:6" ht="16.5">
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1"/>
+    <hyperlink ref="C8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
+  <dimension ref="A1:BC2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:55">
       <c r="B1">
         <v>2017</v>
       </c>
@@ -989,10 +864,70 @@
       <c r="AI1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:35">
+      <c r="AJ1">
+        <v>2051</v>
+      </c>
+      <c r="AK1">
+        <v>2052</v>
+      </c>
+      <c r="AL1">
+        <v>2053</v>
+      </c>
+      <c r="AM1">
+        <v>2054</v>
+      </c>
+      <c r="AN1">
+        <v>2055</v>
+      </c>
+      <c r="AO1">
+        <v>2056</v>
+      </c>
+      <c r="AP1">
+        <v>2057</v>
+      </c>
+      <c r="AQ1">
+        <v>2058</v>
+      </c>
+      <c r="AR1">
+        <v>2059</v>
+      </c>
+      <c r="AS1">
+        <v>2060</v>
+      </c>
+      <c r="AT1">
+        <v>2061</v>
+      </c>
+      <c r="AU1">
+        <v>2062</v>
+      </c>
+      <c r="AV1">
+        <v>2063</v>
+      </c>
+      <c r="AW1">
+        <v>2064</v>
+      </c>
+      <c r="AX1">
+        <v>2065</v>
+      </c>
+      <c r="AY1">
+        <v>2066</v>
+      </c>
+      <c r="AZ1">
+        <v>2067</v>
+      </c>
+      <c r="BA1">
+        <v>2068</v>
+      </c>
+      <c r="BB1">
+        <v>2069</v>
+      </c>
+      <c r="BC1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" s="6">
         <f>Calculations!$A$15</f>
@@ -1127,6 +1062,86 @@
         <v>35476077852.368416</v>
       </c>
       <c r="AI2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AJ2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AK2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AL2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AM2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AN2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AO2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AP2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AQ2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AR2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AS2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AT2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AU2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AV2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AW2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AX2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AY2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="AZ2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="BA2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="BB2" s="6">
+        <f>Calculations!$A$15</f>
+        <v>35476077852.368416</v>
+      </c>
+      <c r="BC2" s="6">
         <f>Calculations!$A$15</f>
         <v>35476077852.368416</v>
       </c>
@@ -1134,4 +1149,165 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA9A2D4F-7FF7-4999-A3B9-D7ED148FA1BC}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CD51863-A7CB-4B11-8FFA-99B819E49715}"/>
 </file>